--- a/data/google_news_dedup_audit_21_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_21_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,610 +445,169 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7584785223007202</v>
+        <v>0.832186222076416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Amazon and Winn-Dixie expand grocery delivery across Florida - The Florida Times-Union</t>
+          <t>FedEx and IIT Madras complete Bengaluru drone delivery trial, explore future of urban logistics - Storyboard18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Winn-Dixie and Amazon partner to deliver groceries. Is your Miami store on board? - Miami Herald</t>
+          <t>FedEx conducts India's first intra-city drone delivery trials in Bengaluru - Mint</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6928025484085083</v>
+        <v>0.8384321928024292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mediaonderzoek Maastricht: De Limburger weer op 1 - De Limburger</t>
+          <t>FedEx and IIT Madras complete Bengaluru drone delivery trial, explore future of urban logistics - Storyboard18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Minderjarig meisje overleden bij steekpartij in Blerick - De Limburger</t>
+          <t>FedEx completes India's first intra-city drone delivery flight trials in Bengaluru - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7313568592071533</v>
+        <v>0.7512423992156982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mediaonderzoek Maastricht: De Limburger weer op 1 - De Limburger</t>
+          <t>Politie treft jachtgeweer aan bij huiszoeking voor drugshandel in Schaarbeek - BRUZZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Steekpartij Blerick - De Limburger</t>
+          <t>Twee verdachten ingerekend voor drugsverkoop in Schaarbeek - Nieuwsblad</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>0.867052435874939</v>
+        <v>0.7009496688842773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Forse vertraging op A2 vanwege eenzijdig ongeval bij vliegveld Beek, automobilist gewond - De Limburger</t>
+          <t>Investigation launched after two injured in Bromley stabbing - London Now</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Forse vertraging op A2 vanwege ongeval bij vliegveld Beek - De Limburger</t>
+          <t>Two people taken to hospital after stabbing in Bromley - London Now</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8219374418258667</v>
+        <v>0.6303766965866089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Negentiger zwaargewond bij ongeval in Hasselt - HBVL</t>
+          <t>London tube strike and the Victoria Line, Tuesday 21st April 2026 – status updates - Brixton Buzz</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negentiger zwaargewond bij ongeval in Hasselt - Nieuwsblad</t>
+          <t>London Tube Strike Set to Cause Travel Chaos for Commuters - Bloomberg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7444247007369995</v>
+        <v>0.8049432039260864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cinema ZED Hasselt toont film over dagelijks leven in Iran met persoonlijke inkijk van Iraanse sprekers - HLN</t>
+          <t>London tube strike and the Victoria Line, Tuesday 21st April 2026 – status updates - Brixton Buzz</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>“Op één jaar tijd stond mijn leven op zijn kop”: olympiër Michael Somers komt met pakkende documentaire naar Cinema ZED in Hasselt - HLN</t>
+          <t>London Tube strike— When disruption starts and which lines are affected - London Now</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7186715602874756</v>
+        <v>0.6855900287628174</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pas getrouwd: Beatrice en Ghislain in Hasselt - HBVL</t>
+          <t>London tube strike and the Victoria Line, Tuesday 21st April 2026 – status updates - Brixton Buzz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pas getrouwd: Skye en Veerle in Hasselt - HBVL</t>
+          <t>London Tube strike: Major disruption across lines as drivers walk out over 4-day work week - The Times of India</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8011385202407837</v>
+        <v>0.6216430068016052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pas getrouwd: Beatrice en Ghislain in Hasselt - HBVL</t>
+          <t>London tube strike and the Victoria Line, Tuesday 21st April 2026 – status updates - Brixton Buzz</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pas getrouwd: Arne en Sara in Hasselt - HBVL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>54</v>
-      </c>
-      <c r="B10" t="n">
-        <v>67</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.9683870077133179</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Pasar Lanaken bezoekt het Nostalgie-museum in Uikhoven - HBVL</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Pasar Lanaken bezoekt het Nostalgie-museum in Uikhoven - Nieuwsblad</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>57</v>
-      </c>
-      <c r="B11" t="n">
-        <v>66</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.9667231440544128</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OKRA Beek ontdekt duurzame logistiek bij Hamelers Palletten in Maasmechelen - HBVL</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>OKRA Beek ontdekt duurzame logistiek bij Hamelers Palletten in Maasmechelen - Nieuwsblad</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>77</v>
-      </c>
-      <c r="B12" t="n">
-        <v>78</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8221760988235474</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Red Hat Day honors, celebrates FSU’s Wertheim College namesake - Florida State University News</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Wertheim College of Business Hosts Red Hat Day - Florida State University News</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>93</v>
-      </c>
-      <c r="B13" t="n">
-        <v>94</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.7684130668640137</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Poisoned baby food jars found in three EU countries part of attempted extortion of company, producer says - The Irish Independent</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Poisoned baby food was part of attempted extortion, German producer says - ARY News</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>106</v>
-      </c>
-      <c r="B14" t="n">
-        <v>108</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.6669285297393799</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>London Tube driver strike to begin at midday - BBC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Tube strikes: how disruptive will action by London Underground drivers be? - The Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>106</v>
-      </c>
-      <c r="B15" t="n">
-        <v>109</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.692357063293457</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>London Tube driver strike to begin at midday - BBC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>London Tube Strike Set to Cause Travel Chaos for Commuters - Bloomberg.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>106</v>
-      </c>
-      <c r="B16" t="n">
-        <v>111</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.7224211692810059</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>London Tube driver strike to begin at midday - BBC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
           <t>Tube strike hits London as Greens accused of backing 'RMT wreckers over workers' - London Evening Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>106</v>
-      </c>
-      <c r="B17" t="n">
-        <v>113</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.5760761499404907</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>London Tube driver strike to begin at midday - BBC</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>London Tube strike: Everything you need to know about lines, times and travel options - Daily Express</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>106</v>
-      </c>
-      <c r="B18" t="n">
-        <v>120</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6869267821311951</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>London Tube driver strike to begin at midday - BBC</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Tube and bus strikes to hit London this week — here’s what you need to know - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>106</v>
-      </c>
-      <c r="B19" t="n">
-        <v>124</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.5697405338287354</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>London Tube driver strike to begin at midday - BBC</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Is Elizabeth line affected by April 2026 Tube strike? - My London</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>106</v>
-      </c>
-      <c r="B20" t="n">
-        <v>125</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.5259233713150024</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>London Tube driver strike to begin at midday - BBC</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>London Tube Strike: The Cost of Transit Instability - streamlinefeed.co.ke</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>106</v>
-      </c>
-      <c r="B21" t="n">
-        <v>126</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6315658092498779</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>London Tube driver strike to begin at midday - BBC</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Tube strike latest - Tube lines affected and will London Underground strikes be cancelled? - Daily Express</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>110</v>
-      </c>
-      <c r="B22" t="n">
-        <v>119</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.7137953042984009</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Anti-Islam influencer blocked from entering UK for Tommy Robinson rally - ITVX</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Anti-Islam agitator and Tommy Robinson ally banned from the UK - The National Scot</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>121</v>
-      </c>
-      <c r="B23" t="n">
-        <v>122</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.8172892332077026</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Islamophobic Quran burner Valentina Gomez banned from entering UK for far-right rally - 5Pillars</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Anti-Islam influencer Valentina Gomez blocked from entering UK for far-right rally - The Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>132</v>
-      </c>
-      <c r="B24" t="n">
-        <v>133</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.7941607236862183</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>In Aula a Milano scoppia la protesta proPal contro il gemellaggio con Tel Aviv - il Giornale</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Milano, caos in Consiglio comunale sul gemellaggio con Tel Aviv: proteste e spaccatura nella maggioranza - TGLA7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>132</v>
-      </c>
-      <c r="B25" t="n">
-        <v>134</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.7114428877830505</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>In Aula a Milano scoppia la protesta proPal contro il gemellaggio con Tel Aviv - il Giornale</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Blitz dei ProPal a Palazzo Marino: "No al gemellaggio tra Milano e Tel Aviv". Seduta sospesa. Il video - MilanoToday</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>132</v>
-      </c>
-      <c r="B26" t="n">
-        <v>135</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.7038849592208862</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>In Aula a Milano scoppia la protesta proPal contro il gemellaggio con Tel Aviv - il Giornale</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MILANO: MOBILITAZIONE IN PIAZZA E IN CONSIGLIO COMUNALE CONTRO IL GEMELLAGGIO CON TEL AVIV - Radio Onda d`Urto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>143</v>
-      </c>
-      <c r="B27" t="n">
-        <v>144</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.7464058399200439</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Valley Forge High School student dies from self-inflicted gunshot wound | Hindustan Times - Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Student dies after shooting herself in cafeteria of Valley Forge High School - Cleveland 19 News</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>143</v>
-      </c>
-      <c r="B28" t="n">
-        <v>145</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.8071311116218567</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Valley Forge High School student dies from self-inflicted gunshot wound | Hindustan Times - Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Valley Forge student dies after shooting self at school; classes canceled - Cleveland.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>143</v>
-      </c>
-      <c r="B29" t="n">
-        <v>146</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.4951440393924713</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Valley Forge High School student dies from self-inflicted gunshot wound | Hindustan Times - Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>‘Still processing what I saw’: Senior speaks out after Valley Forge High School shooting - FOX 8 News</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>143</v>
-      </c>
-      <c r="B30" t="n">
-        <v>147</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.8559918403625488</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Valley Forge High School student dies from self-inflicted gunshot wound | Hindustan Times - Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Valley Forge High School shooting: Student dies from self-inflicted gunshot wound, school confirms - FOX 8 News</t>
         </is>
       </c>
     </row>
